--- a/BeatnotePostHotCell/Jun16,2026/Fit_ResultJun16.xlsx
+++ b/BeatnotePostHotCell/Jun16,2026/Fit_ResultJun16.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wolfwalker\Documents\git\6s7p\BeatnotePostHotCell\Jun16,2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\BeatnotePostHotCell\Jun16,2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C63C78CA-407B-4E40-B424-42CB55638B3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{416E62A2-1622-462B-857B-4E0EA9D009EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{D9E101C5-8284-4B59-8B1C-2AD2D5F2FDD3}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{D9E101C5-8284-4B59-8B1C-2AD2D5F2FDD3}"/>
   </bookViews>
   <sheets>
     <sheet name="894" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="34">
   <si>
     <t>Date</t>
   </si>
@@ -141,25 +141,13 @@
   </si>
   <si>
     <t>Jun16,2026+6-32-11PM</t>
-  </si>
-  <si>
-    <t>Jun16,2026+2-19-36PM</t>
-  </si>
-  <si>
-    <t>Jun16,2026+3-11-44PM</t>
-  </si>
-  <si>
-    <t>Jun16,2026+3-23-47PM</t>
-  </si>
-  <si>
-    <t>Jun16,2026+5-15-57PM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -531,9 +519,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40C5617D-2BBC-4C21-ADC4-3687FEC8C6E3}">
   <dimension ref="A1:S33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -566,7 +554,7 @@
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
     </row>
-    <row r="2" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" ht="42.75">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -591,7 +579,7 @@
       <c r="H2" s="1"/>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" ht="42.75">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -616,7 +604,7 @@
       <c r="H3" s="1"/>
       <c r="S3" s="1"/>
     </row>
-    <row r="4" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" ht="42.75">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -641,7 +629,7 @@
       <c r="H4" s="1"/>
       <c r="S4" s="1"/>
     </row>
-    <row r="5" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" ht="42.75">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -666,7 +654,7 @@
       <c r="H5" s="1"/>
       <c r="S5" s="1"/>
     </row>
-    <row r="6" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" ht="42.75">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -691,7 +679,7 @@
       <c r="H6" s="1"/>
       <c r="S6" s="1"/>
     </row>
-    <row r="7" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" ht="42.75">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -716,7 +704,7 @@
       <c r="H7" s="1"/>
       <c r="S7" s="1"/>
     </row>
-    <row r="8" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" ht="42.75">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
@@ -741,7 +729,7 @@
       <c r="H8" s="1"/>
       <c r="S8" s="1"/>
     </row>
-    <row r="9" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" ht="42.75">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
@@ -766,7 +754,7 @@
       <c r="H9" s="1"/>
       <c r="S9" s="1"/>
     </row>
-    <row r="10" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" ht="42.75">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -791,7 +779,7 @@
       <c r="H10" s="1"/>
       <c r="S10" s="1"/>
     </row>
-    <row r="11" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" ht="42.75">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -815,7 +803,7 @@
       </c>
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" ht="42.75">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
@@ -839,7 +827,7 @@
       </c>
       <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" ht="42.75">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
@@ -863,7 +851,7 @@
       </c>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" ht="42.75">
       <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
@@ -888,7 +876,7 @@
       <c r="H14" s="1"/>
       <c r="R14" s="1"/>
     </row>
-    <row r="15" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" ht="42.75">
       <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
@@ -913,7 +901,7 @@
       <c r="H15" s="1"/>
       <c r="R15" s="1"/>
     </row>
-    <row r="16" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" ht="42.75">
       <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
@@ -938,7 +926,7 @@
       <c r="H16" s="1"/>
       <c r="R16" s="1"/>
     </row>
-    <row r="17" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="42.75">
       <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
@@ -962,7 +950,7 @@
       </c>
       <c r="H17" s="1"/>
     </row>
-    <row r="18" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="42.75">
       <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
@@ -986,7 +974,7 @@
       </c>
       <c r="H18" s="1"/>
     </row>
-    <row r="19" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="42.75">
       <c r="A19" s="1" t="s">
         <v>28</v>
       </c>
@@ -1010,7 +998,7 @@
       </c>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="42.75">
       <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
@@ -1034,7 +1022,7 @@
       </c>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="42.75">
       <c r="A21" s="1" t="s">
         <v>30</v>
       </c>
@@ -1058,7 +1046,7 @@
       </c>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="42.75">
       <c r="A22" s="1" t="s">
         <v>31</v>
       </c>
@@ -1082,7 +1070,7 @@
       </c>
       <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="42.75">
       <c r="A23" s="1" t="s">
         <v>32</v>
       </c>
@@ -1106,7 +1094,7 @@
       </c>
       <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="42.75">
       <c r="A24" s="1" t="s">
         <v>33</v>
       </c>
@@ -1130,7 +1118,7 @@
       </c>
       <c r="H24" s="1"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1139,7 +1127,7 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1148,7 +1136,7 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1157,7 +1145,7 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1166,7 +1154,7 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1175,7 +1163,7 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1184,7 +1172,7 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1193,7 +1181,7 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1202,7 +1190,7 @@
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1219,9 +1207,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{011646E0-737D-49FA-A2CA-7848F848076B}">
   <dimension ref="A1:T40"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1258,12 +1246,12 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
     </row>
-    <row r="2" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" ht="42.75">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="1">
-        <v>0.25402214979933802</v>
+        <v>0.197795261805772</v>
       </c>
       <c r="C2" s="1">
         <v>1.52142266565955</v>
@@ -1275,694 +1263,630 @@
         <v>-1.5491269480861599E-4</v>
       </c>
       <c r="F2" s="1">
-        <v>3.7280379805304502</v>
+        <v>3.6668447136625599</v>
       </c>
       <c r="G2" s="1">
-        <v>40.355064337282897</v>
+        <v>40.349710734935996</v>
       </c>
       <c r="H2" s="1">
-        <v>6.8994874363698805E-4</v>
+        <v>5.7857693786277098E-4</v>
       </c>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" ht="42.75">
       <c r="A3" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1">
-        <v>0.25372210135906698</v>
+        <v>0.19636764328003201</v>
       </c>
       <c r="C3" s="1">
-        <v>1.5219784122537601</v>
+        <v>1.5256163694112701</v>
       </c>
       <c r="D3" s="1">
-        <v>3.0600283973815702E-3</v>
+        <v>2.1195620841066702E-3</v>
       </c>
       <c r="E3" s="1">
-        <v>-2.31553141444368E-4</v>
+        <v>-1.4687830548271901E-4</v>
       </c>
       <c r="F3" s="1">
-        <v>3.7233644055570498</v>
+        <v>2.41845077563696</v>
       </c>
       <c r="G3" s="1">
-        <v>40.3572157900036</v>
+        <v>40.393214429742997</v>
       </c>
       <c r="H3" s="1">
-        <v>5.7857693450234999E-4</v>
+        <v>7.2891784097113099E-4</v>
       </c>
       <c r="S3" s="1"/>
     </row>
-    <row r="4" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" ht="42.75">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1">
-        <v>0.25207440807669201</v>
+        <v>0.199763540533482</v>
       </c>
       <c r="C4" s="1">
-        <v>1.5256163694112701</v>
+        <v>1.5207453861726801</v>
       </c>
       <c r="D4" s="1">
-        <v>2.1195620841066702E-3</v>
+        <v>3.1757544411434302E-3</v>
       </c>
       <c r="E4" s="1">
-        <v>-1.4687830548271901E-4</v>
+        <v>-2.2582991667535201E-4</v>
       </c>
       <c r="F4" s="1">
-        <v>2.4796613642528702</v>
+        <v>3.6659883892748999</v>
       </c>
       <c r="G4" s="1">
-        <v>40.389874591219801</v>
+        <v>40.478915515471201</v>
       </c>
       <c r="H4" s="1">
-        <v>5.8285989468844705E-4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.7857834595978204E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="42.75">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1">
-        <v>0.25648835225167999</v>
+        <v>0.199521024785556</v>
       </c>
       <c r="C5" s="1">
-        <v>1.5207453861726801</v>
+        <v>1.5252866641551499</v>
       </c>
       <c r="D5" s="1">
-        <v>3.1757544411434302E-3</v>
+        <v>2.28458485812892E-3</v>
       </c>
       <c r="E5" s="1">
-        <v>-2.2582991667535201E-4</v>
+        <v>-1.95128756862959E-4</v>
       </c>
       <c r="F5" s="1">
-        <v>3.7271723210188501</v>
+        <v>2.1671169839525599</v>
       </c>
       <c r="G5" s="1">
-        <v>40.382431119225998</v>
+        <v>40.404406310025202</v>
       </c>
       <c r="H5" s="1">
-        <v>5.7857693641636895E-4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.7857693432054901E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="42.75">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1">
-        <v>0.25619702232418301</v>
+        <v>0.20007723541863701</v>
       </c>
       <c r="C6" s="1">
-        <v>1.5252866641551499</v>
+        <v>1.52554305396736</v>
       </c>
       <c r="D6" s="1">
-        <v>2.28458485812892E-3</v>
-      </c>
-      <c r="E6" s="1">
-        <v>-1.95128756862959E-4</v>
+        <v>1.47495664995383E-3</v>
+      </c>
+      <c r="E6" s="2">
+        <v>-3.04149896076687E-5</v>
       </c>
       <c r="F6" s="1">
-        <v>2.2283156443346499</v>
+        <v>2.16756795748383</v>
       </c>
       <c r="G6" s="1">
-        <v>40.404773972601902</v>
+        <v>40.367941460005298</v>
       </c>
       <c r="H6" s="1">
-        <v>5.8511040295225502E-4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.7857693431704596E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="42.75">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1">
-        <v>0.256904989972564</v>
+        <v>0.19981867055438399</v>
       </c>
       <c r="C7" s="1">
-        <v>1.52554305396736</v>
+        <v>1.52457326933981</v>
       </c>
       <c r="D7" s="1">
-        <v>1.47495664995383E-3</v>
-      </c>
-      <c r="E7" s="2">
-        <v>-3.04149896076687E-5</v>
+        <v>2.3537994202564101E-3</v>
+      </c>
+      <c r="E7" s="1">
+        <v>-1.9730138993349501E-4</v>
       </c>
       <c r="F7" s="1">
-        <v>2.2287406907138299</v>
+        <v>2.1308920078929598</v>
       </c>
       <c r="G7" s="1">
-        <v>40.367951827142299</v>
+        <v>40.327974106606597</v>
       </c>
       <c r="H7" s="1">
-        <v>5.7886057157163697E-4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.9855177463813403E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="42.75">
       <c r="A8" s="1" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1">
-        <v>0.25124084766715599</v>
+        <v>0.198366202574008</v>
       </c>
       <c r="C8" s="1">
-        <v>1.5247957511339401</v>
+        <v>1.52419769523953</v>
       </c>
       <c r="D8" s="1">
-        <v>2.08280582010415E-3</v>
+        <v>1.9906546109762801E-3</v>
       </c>
       <c r="E8" s="1">
-        <v>-1.5546471536574401E-4</v>
+        <v>-1.18831906476894E-4</v>
       </c>
       <c r="F8" s="1">
-        <v>2.2250675917832901</v>
+        <v>2.1297680198394899</v>
       </c>
       <c r="G8" s="1">
-        <v>40.358074627858599</v>
+        <v>40.321513700000303</v>
       </c>
       <c r="H8" s="1">
-        <v>6.5966071823058998E-4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.7857693432016705E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="42.75">
       <c r="A9" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1">
-        <v>0.25175581616731701</v>
+        <v>0.199095753907192</v>
       </c>
       <c r="C9" s="1">
-        <v>1.52508462911658</v>
+        <v>1.5244558472980201</v>
       </c>
       <c r="D9" s="1">
-        <v>1.9295536703228099E-3</v>
-      </c>
-      <c r="E9" s="1">
-        <v>-1.2305647579486401E-4</v>
+        <v>1.8717692091512E-3</v>
+      </c>
+      <c r="E9" s="2">
+        <v>-9.4761135365893797E-5</v>
       </c>
       <c r="F9" s="1">
-        <v>2.22614219174966</v>
+        <v>1.91430512987475</v>
       </c>
       <c r="G9" s="1">
-        <v>40.341220900099103</v>
+        <v>40.317212554401202</v>
       </c>
       <c r="H9" s="1">
-        <v>5.7857693431967005E-4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.7857693645732902E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="42.75">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B10" s="1">
-        <v>0.25656545981822299</v>
+        <v>0.204499456522232</v>
       </c>
       <c r="C10" s="1">
-        <v>1.52457326933981</v>
+        <v>1.5231646737669799</v>
       </c>
       <c r="D10" s="1">
-        <v>2.3537994202564101E-3</v>
+        <v>2.5677935934539302E-3</v>
       </c>
       <c r="E10" s="1">
-        <v>-1.9730138993349501E-4</v>
+        <v>-2.1128884830732799E-4</v>
       </c>
       <c r="F10" s="1">
-        <v>2.1920731991690099</v>
+        <v>2.37601741737909</v>
       </c>
       <c r="G10" s="1">
-        <v>40.327981759617501</v>
+        <v>42.163737959880201</v>
       </c>
       <c r="H10" s="1">
-        <v>5.7904347837242902E-4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.7869419200762902E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="42.75">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B11" s="1">
-        <v>0.25471437628790899</v>
+        <v>0.20177332786484001</v>
       </c>
       <c r="C11" s="1">
-        <v>1.52419769523953</v>
+        <v>1.52468814428226</v>
       </c>
       <c r="D11" s="1">
-        <v>1.9906546109762801E-3</v>
+        <v>2.0898180420625598E-3</v>
       </c>
       <c r="E11" s="1">
-        <v>-1.18831906476894E-4</v>
+        <v>-1.7983278653885599E-4</v>
       </c>
       <c r="F11" s="1">
-        <v>2.1909626337888599</v>
+        <v>1.91327489596684</v>
       </c>
       <c r="G11" s="1">
-        <v>40.321713305251102</v>
+        <v>42.259611984733297</v>
       </c>
       <c r="H11" s="1">
-        <v>5.8090027549205601E-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.03709070366766E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="42.75">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1">
-        <v>0.25564492601438199</v>
+        <v>0.19953623295292</v>
       </c>
       <c r="C12" s="1">
-        <v>1.5244558472980201</v>
+        <v>1.52460507111515</v>
       </c>
       <c r="D12" s="1">
-        <v>1.8717692091512E-3</v>
-      </c>
-      <c r="E12" s="2">
-        <v>-9.4761135365893797E-5</v>
+        <v>2.31041460234931E-3</v>
+      </c>
+      <c r="E12" s="1">
+        <v>-2.2098654240545101E-4</v>
       </c>
       <c r="F12" s="1">
-        <v>1.9755070237641501</v>
+        <v>1.92286693065935</v>
       </c>
       <c r="G12" s="1">
-        <v>40.317212994884997</v>
+        <v>40.273989576232402</v>
       </c>
       <c r="H12" s="1">
-        <v>5.7875689422114596E-4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.7857693593742199E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="42.75">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1">
-        <v>0.26266359379455601</v>
+        <v>0.20147692004263501</v>
       </c>
       <c r="C13" s="1">
-        <v>1.5231646737669799</v>
+        <v>1.5219959632098701</v>
       </c>
       <c r="D13" s="1">
-        <v>2.5677935934539302E-3</v>
+        <v>2.23052649479421E-3</v>
       </c>
       <c r="E13" s="1">
-        <v>-2.1128884830732799E-4</v>
+        <v>-1.2469443073558501E-4</v>
       </c>
       <c r="F13" s="1">
-        <v>2.4371705502249101</v>
+        <v>3.16273347642541</v>
       </c>
       <c r="G13" s="1">
-        <v>42.309774382457597</v>
+        <v>42.207800972082197</v>
       </c>
       <c r="H13" s="1">
-        <v>6.9994445573110604E-4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.156494932738E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="42.75">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1">
-        <v>0.25914186884267898</v>
+        <v>0.20099134894088699</v>
       </c>
       <c r="C14" s="1">
-        <v>1.52468814428226</v>
+        <v>1.52084454539931</v>
       </c>
       <c r="D14" s="1">
-        <v>2.0898180420625598E-3</v>
+        <v>2.5927816987614699E-3</v>
       </c>
       <c r="E14" s="1">
-        <v>-1.7983278653885599E-4</v>
+        <v>-1.6139932324158601E-4</v>
       </c>
       <c r="F14" s="1">
-        <v>1.9744262668644801</v>
+        <v>3.42111626351732</v>
       </c>
       <c r="G14" s="1">
-        <v>42.297243069022102</v>
+        <v>40.226035720523498</v>
       </c>
       <c r="H14" s="1">
-        <v>1.1571538679983999E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7.1778766975387205E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="42.75">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B15" s="1">
-        <v>0.25621155685651098</v>
+        <v>0.20205758915667599</v>
       </c>
       <c r="C15" s="1">
-        <v>1.52460507111515</v>
+        <v>1.5214179701261099</v>
       </c>
       <c r="D15" s="1">
-        <v>2.31041460234931E-3</v>
+        <v>2.69327479283266E-3</v>
       </c>
       <c r="E15" s="1">
-        <v>-2.2098654240545101E-4</v>
+        <v>-1.8007498712088401E-4</v>
       </c>
       <c r="F15" s="1">
-        <v>1.9840602940061001</v>
+        <v>3.16051316376124</v>
       </c>
       <c r="G15" s="1">
-        <v>40.273989570114303</v>
+        <v>42.185404468265602</v>
       </c>
       <c r="H15" s="1">
-        <v>5.7857693435434099E-4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.1511760248688E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="42.75">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B16" s="1">
-        <v>0.25866494788723898</v>
+        <v>0.19732734762757201</v>
       </c>
       <c r="C16" s="1">
-        <v>1.5219959632098701</v>
+        <v>1.5220922143876601</v>
       </c>
       <c r="D16" s="1">
-        <v>2.23052649479421E-3</v>
+        <v>2.3968668449893902E-3</v>
       </c>
       <c r="E16" s="1">
-        <v>-1.2469443073558501E-4</v>
+        <v>-1.4730132493353699E-4</v>
       </c>
       <c r="F16" s="1">
-        <v>3.2239250438699099</v>
+        <v>3.1678893681944902</v>
       </c>
       <c r="G16" s="1">
-        <v>42.199085686275303</v>
+        <v>40.164939309697701</v>
       </c>
       <c r="H16" s="1">
-        <v>1.08708722300643E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.9243382189198E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="42.75">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B17" s="1">
-        <v>0.25801756322347102</v>
+        <v>0.203672875007014</v>
       </c>
       <c r="C17" s="1">
-        <v>1.52084454539931</v>
+        <v>1.52073997246879</v>
       </c>
       <c r="D17" s="1">
-        <v>2.5927816987614699E-3</v>
+        <v>2.8088085965540101E-3</v>
       </c>
       <c r="E17" s="1">
-        <v>-1.6139932324158601E-4</v>
+        <v>-1.93396547650335E-4</v>
       </c>
       <c r="F17" s="1">
-        <v>3.4823004035062599</v>
+        <v>3.41659567122365</v>
       </c>
       <c r="G17" s="1">
-        <v>40.220311594406297</v>
+        <v>42.153619496046403</v>
       </c>
       <c r="H17" s="1">
-        <v>5.7857693531042495E-4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.0752527426079201E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="42.75">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B18" s="1">
-        <v>0.25944545650678502</v>
+        <v>0.202463132614286</v>
       </c>
       <c r="C18" s="1">
-        <v>1.5214179701261099</v>
+        <v>1.5212750464160401</v>
       </c>
       <c r="D18" s="1">
-        <v>2.69327479283266E-3</v>
+        <v>2.8973057717686899E-3</v>
       </c>
       <c r="E18" s="1">
-        <v>-1.8007498712088401E-4</v>
+        <v>-2.3249208487534701E-4</v>
       </c>
       <c r="F18" s="1">
-        <v>3.2216802433967899</v>
+        <v>3.1666975803124999</v>
       </c>
       <c r="G18" s="1">
-        <v>42.185516269408303</v>
+        <v>41.348812425661102</v>
       </c>
       <c r="H18" s="1">
-        <v>1.1571538502001999E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.3631481844115797E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="42.75">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B19" s="1">
-        <v>0.25336488450504602</v>
+        <v>0.201204039279366</v>
       </c>
       <c r="C19" s="1">
-        <v>1.5220922143876601</v>
+        <v>1.5221706928363901</v>
       </c>
       <c r="D19" s="1">
-        <v>2.3968668449893902E-3</v>
+        <v>2.3458078217860599E-3</v>
       </c>
       <c r="E19" s="1">
-        <v>-1.4730132493353699E-4</v>
+        <v>-1.4210581012311899E-4</v>
       </c>
       <c r="F19" s="1">
-        <v>3.2291059385919101</v>
+        <v>3.16616260906159</v>
       </c>
       <c r="G19" s="1">
-        <v>40.162990145435401</v>
+        <v>40.178136340681696</v>
       </c>
       <c r="H19" s="1">
-        <v>5.79197835338322E-4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.9316481203990697E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="42.75">
       <c r="A20" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B20" s="1">
-        <v>0.26620927592495203</v>
+        <v>0.19871515752240099</v>
       </c>
       <c r="C20" s="1">
-        <v>1.52177650962274</v>
+        <v>1.52174978486126</v>
       </c>
       <c r="D20" s="1">
-        <v>2.6535439827002098E-3</v>
+        <v>2.79098205910241E-3</v>
       </c>
       <c r="E20" s="1">
-        <v>-1.93028836575936E-4</v>
+        <v>-2.1937542886835501E-4</v>
       </c>
       <c r="F20" s="1">
-        <v>3.2307961065169102</v>
+        <v>3.1674617209715499</v>
       </c>
       <c r="G20" s="1">
-        <v>42.1711284069507</v>
+        <v>40.092242482633502</v>
       </c>
       <c r="H20" s="1">
-        <v>1.1571538670001899E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.8489520761039002E-4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="42.75">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B21" s="1">
-        <v>0.261553420142073</v>
+        <v>0.19699200110692699</v>
       </c>
       <c r="C21" s="1">
-        <v>1.52073997246879</v>
+        <v>1.5221088454787799</v>
       </c>
       <c r="D21" s="1">
-        <v>2.8088085965540101E-3</v>
+        <v>2.2554249637675699E-3</v>
       </c>
       <c r="E21" s="1">
-        <v>-1.93396547650335E-4</v>
+        <v>-1.2441511141059801E-4</v>
       </c>
       <c r="F21" s="1">
-        <v>3.4777561657126301</v>
+        <v>3.1728547423956099</v>
       </c>
       <c r="G21" s="1">
-        <v>42.152614810957097</v>
+        <v>40.067835498966801</v>
       </c>
       <c r="H21" s="1">
-        <v>1.1481465052756001E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.7857697561696799E-4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="42.75">
       <c r="A22" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B22" s="1">
-        <v>0.26019522603942802</v>
+        <v>0.19973329976234899</v>
       </c>
       <c r="C22" s="1">
-        <v>1.5212750464160401</v>
+        <v>1.5209218180648001</v>
       </c>
       <c r="D22" s="1">
-        <v>2.8973057717686899E-3</v>
+        <v>3.1385618233413502E-3</v>
       </c>
       <c r="E22" s="1">
-        <v>-2.3249208487534701E-4</v>
+        <v>-2.4909142340594898E-4</v>
       </c>
       <c r="F22" s="1">
-        <v>3.2278910147729998</v>
+        <v>3.4207621305520099</v>
       </c>
       <c r="G22" s="1">
-        <v>42.127872215443602</v>
+        <v>40.3200686396371</v>
       </c>
       <c r="H22" s="1">
-        <v>8.6098583064988295E-4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.0832228595084201E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="42.75">
       <c r="A23" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B23" s="1">
-        <v>0.25868729407005198</v>
+        <v>0.201359161151828</v>
       </c>
       <c r="C23" s="1">
-        <v>1.5221706928363901</v>
+        <v>1.5211404087095299</v>
       </c>
       <c r="D23" s="1">
-        <v>2.3458078217860599E-3</v>
+        <v>2.72049198184519E-3</v>
       </c>
       <c r="E23" s="1">
-        <v>-1.4210581012311899E-4</v>
+        <v>-1.8944287980608799E-4</v>
       </c>
       <c r="F23" s="1">
-        <v>3.2273478694720299</v>
+        <v>3.3777530214716101</v>
       </c>
       <c r="G23" s="1">
-        <v>42.1436347848</v>
+        <v>41.868617673014803</v>
       </c>
       <c r="H23" s="1">
-        <v>6.0423997904261696E-4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.9719734863382704E-4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="42.75">
       <c r="A24" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B24" s="1">
-        <v>0.25516460879894798</v>
+        <v>0.19777927876332499</v>
       </c>
       <c r="C24" s="1">
-        <v>1.52174978486126</v>
+        <v>1.52178365430753</v>
       </c>
       <c r="D24" s="1">
-        <v>2.79098205910241E-3</v>
+        <v>2.49623631854349E-3</v>
       </c>
       <c r="E24" s="1">
-        <v>-2.1937542886835501E-4</v>
+        <v>-1.73234994111277E-4</v>
       </c>
       <c r="F24" s="1">
-        <v>3.2286316522314</v>
+        <v>3.16497079622029</v>
       </c>
       <c r="G24" s="1">
-        <v>40.119395703495897</v>
+        <v>40.051826226974299</v>
       </c>
       <c r="H24" s="1">
-        <v>5.9132413792382205E-4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="1">
-        <v>0.25295075090609098</v>
-      </c>
-      <c r="C25" s="1">
-        <v>1.5221088454787799</v>
-      </c>
-      <c r="D25" s="1">
-        <v>2.2554249637675699E-3</v>
-      </c>
-      <c r="E25" s="1">
-        <v>-1.2441511141059801E-4</v>
-      </c>
-      <c r="F25" s="1">
-        <v>3.2340238094298899</v>
-      </c>
-      <c r="G25" s="1">
-        <v>40.067833909999898</v>
-      </c>
-      <c r="H25" s="1">
-        <v>5.7857693433978796E-4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" s="1">
-        <v>0.256452611497334</v>
-      </c>
-      <c r="C26" s="1">
-        <v>1.5209218180648001</v>
-      </c>
-      <c r="D26" s="1">
-        <v>3.1385618233413502E-3</v>
-      </c>
-      <c r="E26" s="1">
-        <v>-2.4909142340594898E-4</v>
-      </c>
-      <c r="F26" s="1">
-        <v>3.48196348707648</v>
-      </c>
-      <c r="G26" s="1">
-        <v>40.302460583775698</v>
-      </c>
-      <c r="H26" s="1">
-        <v>5.9741117951988003E-4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27" s="1">
-        <v>0.25868777299010298</v>
-      </c>
-      <c r="C27" s="1">
-        <v>1.5211404087095299</v>
-      </c>
-      <c r="D27" s="1">
-        <v>2.72049198184519E-3</v>
-      </c>
-      <c r="E27" s="1">
-        <v>-1.8944287980608799E-4</v>
-      </c>
-      <c r="F27" s="1">
-        <v>3.4389243644236598</v>
-      </c>
-      <c r="G27" s="1">
-        <v>42.056362653752501</v>
-      </c>
-      <c r="H27" s="1">
-        <v>8.3935057304407605E-4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B28" s="1">
-        <v>0.2539674766801</v>
-      </c>
-      <c r="C28" s="1">
-        <v>1.52178365430753</v>
-      </c>
-      <c r="D28" s="1">
-        <v>2.49623631854349E-3</v>
-      </c>
-      <c r="E28" s="1">
-        <v>-1.73234994111277E-4</v>
-      </c>
-      <c r="F28" s="1">
-        <v>3.22615686478124</v>
-      </c>
-      <c r="G28" s="1">
-        <v>40.057064661056302</v>
-      </c>
-      <c r="H28" s="1">
-        <v>6.0959203614837797E-4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+        <v>5.8158129637159704E-4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1972,7 +1896,7 @@
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1982,7 +1906,7 @@
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1992,7 +1916,7 @@
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -2002,7 +1926,7 @@
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -2012,7 +1936,7 @@
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -2022,7 +1946,7 @@
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -2032,7 +1956,7 @@
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -2042,7 +1966,7 @@
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2052,7 +1976,7 @@
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2062,7 +1986,7 @@
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2072,7 +1996,7 @@
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -2089,13 +2013,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF8CB368-1F4F-4C65-B86B-93EC676CB77B}">
-  <dimension ref="A1:G36"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:L40"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="5" max="5" width="16.7265625" customWidth="1"/>
+    <col min="5" max="5" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2105,8 +2029,10 @@
       <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+    </row>
+    <row r="2" spans="1:12" ht="42.75">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -2114,7 +2040,7 @@
         <v>15.893216524612599</v>
       </c>
       <c r="C2" s="1">
-        <v>0.25402214979933802</v>
+        <v>0.197795261805772</v>
       </c>
       <c r="F2">
         <v>894</v>
@@ -2122,8 +2048,9 @@
       <c r="G2">
         <v>456</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="K2" s="1"/>
+    </row>
+    <row r="3" spans="1:12" ht="42.75">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -2131,7 +2058,7 @@
         <v>15.779780400421799</v>
       </c>
       <c r="C3" s="1">
-        <v>0.25207440807669201</v>
+        <v>0.19636764328003201</v>
       </c>
       <c r="E3" t="s">
         <v>1</v>
@@ -2142,10 +2069,11 @@
       </c>
       <c r="G3">
         <f>AVERAGE(C2:C33)</f>
-        <v>0.25686003118632117</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.20001680439888353</v>
+      </c>
+      <c r="K3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" ht="42.75">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -2153,7 +2081,7 @@
         <v>15.7375098014318</v>
       </c>
       <c r="C4" s="1">
-        <v>0.25648835225167999</v>
+        <v>0.199763540533482</v>
       </c>
       <c r="E4" t="s">
         <v>2</v>
@@ -2164,10 +2092,11 @@
       </c>
       <c r="G4">
         <f>_xlfn.STDEV.S(C2:C33)</f>
-        <v>2.7554084058109786E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>2.1166105409287299E-3</v>
+      </c>
+      <c r="K4" s="1"/>
+    </row>
+    <row r="5" spans="1:12" ht="42.75">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -2175,7 +2104,7 @@
         <v>15.644238135424301</v>
       </c>
       <c r="C5" s="1">
-        <v>0.25619702232418301</v>
+        <v>0.199521024785556</v>
       </c>
       <c r="E5" t="s">
         <v>3</v>
@@ -2186,10 +2115,11 @@
       </c>
       <c r="G5">
         <f>G4/G3/SQRT(COUNT(C2:C33))</f>
-        <v>2.2367916353979301E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>2.2065336362870405E-3</v>
+      </c>
+      <c r="K5" s="1"/>
+    </row>
+    <row r="6" spans="1:12" ht="42.75">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -2197,10 +2127,11 @@
         <v>16.0404007362275</v>
       </c>
       <c r="C6" s="1">
-        <v>0.256904989972564</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.20007723541863701</v>
+      </c>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:12" ht="42.75">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -2208,10 +2139,11 @@
         <v>15.526853103393799</v>
       </c>
       <c r="C7" s="1">
-        <v>0.25656545981822299</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.19981867055438399</v>
+      </c>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:12" ht="42.75">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
@@ -2219,10 +2151,11 @@
         <v>15.7036096357806</v>
       </c>
       <c r="C8" s="1">
-        <v>0.25471437628790899</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.198366202574008</v>
+      </c>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:12" ht="42.75">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
@@ -2230,10 +2163,11 @@
         <v>15.562012023522399</v>
       </c>
       <c r="C9" s="1">
-        <v>0.25564492601438199</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.199095753907192</v>
+      </c>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:12" ht="42.75">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -2241,10 +2175,11 @@
         <v>15.913642252075</v>
       </c>
       <c r="C10" s="1">
-        <v>0.26266359379455601</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.204499456522232</v>
+      </c>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="1:12" ht="42.75">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -2252,10 +2187,11 @@
         <v>15.896285735356299</v>
       </c>
       <c r="C11" s="1">
-        <v>0.25914186884267898</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.20177332786484001</v>
+      </c>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:12" ht="42.75">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
@@ -2263,10 +2199,11 @@
         <v>15.958659068376001</v>
       </c>
       <c r="C12" s="1">
-        <v>0.25621155685651098</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.19953623295292</v>
+      </c>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:12" ht="42.75">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
@@ -2274,10 +2211,11 @@
         <v>15.673134901285501</v>
       </c>
       <c r="C13" s="1">
-        <v>0.25866494788723898</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.20147692004263501</v>
+      </c>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:12" ht="42.75">
       <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
@@ -2285,10 +2223,11 @@
         <v>15.850053804713101</v>
       </c>
       <c r="C14" s="1">
-        <v>0.25801756322347102</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.20099134894088699</v>
+      </c>
+      <c r="K14" s="1"/>
+    </row>
+    <row r="15" spans="1:12" ht="42.75">
       <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
@@ -2296,10 +2235,11 @@
         <v>15.8642190956806</v>
       </c>
       <c r="C15" s="1">
-        <v>0.25944545650678502</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.20205758915667599</v>
+      </c>
+      <c r="K15" s="1"/>
+    </row>
+    <row r="16" spans="1:12" ht="42.75">
       <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
@@ -2307,10 +2247,11 @@
         <v>15.9252668940867</v>
       </c>
       <c r="C16" s="1">
-        <v>0.25336488450504602</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.19732734762757201</v>
+      </c>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" spans="1:12" ht="42.75">
       <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
@@ -2318,10 +2259,11 @@
         <v>15.884348606860501</v>
       </c>
       <c r="C17" s="1">
-        <v>0.261553420142073</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.203672875007014</v>
+      </c>
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" spans="1:12" ht="42.75">
       <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
@@ -2329,10 +2271,11 @@
         <v>15.6346331521121</v>
       </c>
       <c r="C18" s="1">
-        <v>0.26019522603942802</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.202463132614286</v>
+      </c>
+      <c r="K18" s="1"/>
+    </row>
+    <row r="19" spans="1:12" ht="42.75">
       <c r="A19" s="1" t="s">
         <v>28</v>
       </c>
@@ -2340,10 +2283,11 @@
         <v>15.818170639051299</v>
       </c>
       <c r="C19" s="1">
-        <v>0.25868729407005198</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.201204039279366</v>
+      </c>
+      <c r="K19" s="1"/>
+    </row>
+    <row r="20" spans="1:12" ht="42.75">
       <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
@@ -2351,10 +2295,11 @@
         <v>15.947264131374601</v>
       </c>
       <c r="C20" s="1">
-        <v>0.25516460879894798</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.19871515752240099</v>
+      </c>
+      <c r="K20" s="1"/>
+    </row>
+    <row r="21" spans="1:12" ht="42.75">
       <c r="A21" s="1" t="s">
         <v>30</v>
       </c>
@@ -2362,10 +2307,11 @@
         <v>15.924948044130501</v>
       </c>
       <c r="C21" s="1">
-        <v>0.25295075090609098</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.19699200110692699</v>
+      </c>
+      <c r="K21" s="1"/>
+    </row>
+    <row r="22" spans="1:12" ht="42.75">
       <c r="A22" s="1" t="s">
         <v>31</v>
       </c>
@@ -2373,10 +2319,11 @@
         <v>15.963192712237699</v>
       </c>
       <c r="C22" s="1">
-        <v>0.256452611497334</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.19973329976234899</v>
+      </c>
+      <c r="K22" s="1"/>
+    </row>
+    <row r="23" spans="1:12" ht="42.75">
       <c r="A23" s="1" t="s">
         <v>32</v>
       </c>
@@ -2384,10 +2331,11 @@
         <v>15.8676552218831</v>
       </c>
       <c r="C23" s="1">
-        <v>0.25868777299010298</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.201359161151828</v>
+      </c>
+      <c r="K23" s="1"/>
+    </row>
+    <row r="24" spans="1:12" ht="42.75">
       <c r="A24" s="1" t="s">
         <v>33</v>
       </c>
@@ -2395,62 +2343,103 @@
         <v>15.928435989248699</v>
       </c>
       <c r="C24" s="1">
-        <v>0.2539674766801</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+        <v>0.19777927876332499</v>
+      </c>
+      <c r="K24" s="1"/>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+    </row>
+    <row r="28" spans="1:12">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+    </row>
+    <row r="29" spans="1:12">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+    </row>
+    <row r="30" spans="1:12">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+    </row>
+    <row r="33" spans="1:12">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+    </row>
+    <row r="34" spans="1:12">
       <c r="C34" s="1"/>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+    </row>
+    <row r="35" spans="1:12">
       <c r="C35" s="1"/>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+    </row>
+    <row r="36" spans="1:12">
       <c r="C36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
